--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SmartCity20\.gemini\antigravity\scratch\surd-lab-homepage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SmartCity20\.gemini\antigravity\scratch\surd-lab-homepage\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829171BF-558E-4460-97A1-5D04B7BFD391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C3F26E-D3DC-4B3D-AEA3-9732C8DDF321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25800" yWindow="0" windowWidth="25800" windowHeight="21000" xr2:uid="{FB3B5A28-B30A-4FB9-B973-DA7691D44842}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{FB3B5A28-B30A-4FB9-B973-DA7691D44842}"/>
   </bookViews>
   <sheets>
     <sheet name="publications" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="604">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,10 +61,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>index_type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>year</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1521,12 +1517,684 @@
   </si>
   <si>
     <t>Y</t>
+  </si>
+  <si>
+    <t>박수빈, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>젠트리피케이션의 부작용 방지를 위한 지역공동체 역할에 관한 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성진욱, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이항로직모형을 이용한 가로주택정비사업 찬반에 미치는 영향요인에 관한 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 프라임 오피스 빌딩의 점유비용 결정요인에 관한 실증분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 시가화지역 유형별 적정개발밀도 산정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이남석, 배효정, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주한미군 반환기지 개발이 주변 아파트가격에 미치는 영향 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도시재생특별법과 도시재생 관련법의 정합성 분석 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정필립, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>외국인직접투자 유치를 위한 경제자유구역 입지 경쟁력 평가에 관한 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>류인정, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 공동주택의 정비유형 선택모형에 따른 유형별 수요와 공간적 분포 특성에 관한 연구: 용적률과 주택가격을 중심으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박수룡, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>택지개발에 따른 대체 산업단지의 이주 결정요인 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박지현, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도시쇠퇴현상이 도시관리비용에 미치는 영향에 관한 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유명소, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소규모 코하우징 거주자의 주거만족도 영향요인에 관한 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>권영필, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>준공업지역의 계획적 관리를 위한 산업기반평가모델 연구 - 서울시 준공업지역을 중심으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 숙박시설의 객실수급 변화양상 및 전망 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부동산학연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업연관분석을 활용한 도시재생사업의 경제적 효과 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이하연, 이지현, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>젠트리피케이션 부작용 방지를 위한 상가임대인 조세지원 제도의 경제적 효용에 관한 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전근철, 남진, 조우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국립공원 구역 조정이 토지이용 변화 및 가격에 끼친 영향 - 월악산국립공원을 중심으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국환경생태학회지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Changhyo Yi, Jin Nam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Interaction Effects between the Agglomerative Externalities Affecting the Survival of Small Startups</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Growth and Change</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SSCI</t>
+  </si>
+  <si>
+    <t>1311-1337</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다층모형을 활용한 개인, 가구, 지역차원에서의 주거만족도에 관한 연구 - 서울시 공공임대주택 사례를 중심으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ki-Wook Song, Byung-Hun Yun, Jin Nam</t>
+  </si>
+  <si>
+    <t>서울시 공공임대주택 주택성능과 주거환경 만족도에 미치는 영향요인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정재훈, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위치기반 빅데이터를 활용한 서울시 활동인구 유형 및 유형별 지역 특성 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이다원, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나눔카 서비스의 교통형평성 평가 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이정현, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Su-Bin Lee, Su-Min Son, Sun-Jeong Kim, Jin Nam</t>
+  </si>
+  <si>
+    <t>서울시 저층주거지의 주택유형별 개발에 미치는 영향요인에 관한 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>35-53</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정성국, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 생활권계획 도입에 대한 효과 분석 - AHP분석을 통한 전문가 설문을 중심으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도시정책연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>167-185</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한지혜, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도시지역 내 산업단지 쇠퇴가 도시 쇠퇴에 미치는 영향 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>167-187</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Byung-Hun Yun, Jin Nam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Development of Evaluation Model of Urban Growth Stage Considering the Connectivity between Core and Periphery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Journal of Urban Planning and Development</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jiyeon Kim, Jin Nam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>An Analysis of the Changing Influence Factors on the Housing Affordability for One-person Tenant in Seoul</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>153-172</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021, Ki-Wook Song, Byung-Hun Yun, Jin Nam, Analysis on the Change Pattern and Dynamic Characteristics of Location Centrality in K-REITs’ Underlying Assets Using the Spatial Statistical Model, KPA 56(1).pdf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Analysis on the Change Pattern and Dynamic Characteristics of Location Centrality in K-REITs’ Underlying Assets Using the Spatial Statistical Model</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021, Su-Bin Lee, Su-Min Son, Sun-Jeong Kim, Jin Nam, Big Data-Based Analysis of Characteristics of Consumption Sales by Region and Age _ Focused on Seoul, KPA 56(2), 138-158.pdf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Big Data-Based Analysis of Characteristics of Consumption Sales by Region and Age - Focused on Seoul</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021, Su-Youn Seong, Jae-Seob Yang, Jin Nam, A Study on the Socio-spatial Characteristics of the Elderly and the Influence Factors of ‘Aging in Place’ in Seoul _ With a Focus on Elderly-concentrated Areas.pdf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Su-Youn Seong, Jae-Seob Yang, Jin Nam</t>
+  </si>
+  <si>
+    <t>A Study on the Socio-spatial Characteristics of the Elderly and the Influence Factors of ‘Aging in Place’ in Seoul _ With a Focus on Elderly-concentrated Areas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김지연, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 1인 임차 가구의 주거비 부담에 미치는 영향 요인 변화 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박인숙, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재개발임대주택의 특성이 주거만족도에 미치는 영향 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>21-40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포용도시 관점에서 재개발임대주택의 사회적 배제 완화를 위한 요인별 중요도 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5-18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성수연, 양재섭, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 고령인구의 사회공간적 특성과 계속 거주 의향에 영향을 미치는 요인 분석 - 고령인구 밀집지역을 중심으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>송기욱, 윤병훈, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공간통계모형을 응용한 부동산투자회사(REITs) 기초자산 입지 중심성 변화 및 동태적 특성 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안성재, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시민의 소비패턴 변화에 따른 도심형 물류창고 입지분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>165-187</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이수빈, 김선정, 손수민, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빅데이터를 활용한 연령별 지역별 소비매출액 특성분석 - 서울시를 중심으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이수빈, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스마트시티 생활서비스의 지역적 특성과 결핍지역 분석 - 서울시 행정동을 중심으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30-43</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 도시공간 중심성의 변화와 그 요인분석 - 2011년과 2019년을 중심으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22-35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장제환, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도시지역과 비도시지역의 생활넃 격차 분석 - 경기도 고양시를 대상으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>199-218</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>권재연, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울대도시권 스타트업 집적지의 유형별 입지 특성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김선정, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도시 네트워크 기반 상호작용의 정도가 주택가격에 미치는 영향분석 - 서울대도시권을 중심으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>157-173</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>손수민, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빅데이터를 활용한 서울시 주거지역 내 소비매출액 변화 및 영향요인 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도시부동산연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>131-159</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이이주, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지역산업연관표에 기반한 국토 공간의 폐기물 투입산출구조 분석 - 수도권을 중심으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재개발사업의 공공성 패러다임 전환에 관한 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정지우, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">빅데이터와 머신러닝을 활용한 스마트 재난관리에 관한 연구 - 서울시 열섬 취약지역을 중심으로 - </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스마트도시건축학회논문집</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20-29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제조업 특화지역에서 지식집약사업서비스업이 지역경제에 미치는 영향</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>71-90</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한영민, 정재훈, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 1인가구 주거이동량과 소형주택 재고량의 지역별 차이 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>115-127</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주거이동 네트워크에 따른 서울대도시권 도시성장단계 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 준공업지역의 산업집적이 지역경제성장에 미치는 영향</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 준공업지역의 산업변화 분석연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29-50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김나래, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주택정비형 재개발사업의 추진단계별 리스크에 따른 사업소요기간 분석연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>147-159</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김성호, 이창효, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 지역별 쇠퇴수준에 따른 음식점 생존율 및 생존요인 실증 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>68-82</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장진하, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여성 주거에 대한 해외 연구의 계량서지학적 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대한건축학회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>108-119</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정재훈, 한영민, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>차별적 도시화 모델에 따른 한국 대도시권 도시성장단계 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>33-47</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 공공임대주택의 특성과 가구의 경제적 향상에 관한 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>104-115</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홍선기, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 도시계획변경 사전협상제도의 변천과정과 도입효과에 관한 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>81-95</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오윤정, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 공공임대주택 거주자의 주거비부담 결정요인 분석 - 장애인과 비장애인 가구의 비교를 중심으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25-45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이광석, 정종대, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 전세보증금 및 전세 레버리지 규모추정 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>109-124</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이창효, 남진, 김진하, 이재수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Comparison of the Distributions of Centrality Indicies - Using Spatial Big Data to Understand Urban Spatial Structure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cities</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1인가구와 소형주택 간의 공간적 관계 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>61-76</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소형주택 공급이 1인가구의 주거입지에 미치는 영향 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조민주, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 상업지역 내 주거 용도 확대가 주변 지역 고용에 미치는 영향에 관한 연구 - 중심지 위계 간 차이를 중심으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5-29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>권예원, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 저층주거지의 청년가구 인큐베이팅 역할에 관한 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70-93</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김창규, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 도심재개발사업의 정책변화 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>송선영, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비수도권 지역특성이 지역발전에 미치는 영향 - 외국인 근로자 유입의 조절 및 매개효과를 중심으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국토연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>127-153</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인구감소지역의 청년인구 이동패턴 및 지역특성 - 비수도권 지역을 중심으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>107-135</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>송정미, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 주택재개발 사업에서 신속통합기획의 특성 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>85-102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 주택유형별 보증금미반환 위험 요인에 관한 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5-27</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KCI</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Report</t>
+  </si>
+  <si>
+    <t>type_index</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1577,13 +2245,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1629,8 +2297,8 @@
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{A3F79930-0951-4BB1-9334-E9583C167FB9}" name="id"/>
     <tableColumn id="2" xr3:uid="{E3831AFD-57F7-42F7-9B92-611D56962AE7}" name="type"/>
-    <tableColumn id="3" xr3:uid="{329E54A5-7737-4A43-B69F-B74CF0504FAA}" name="index_type"/>
-    <tableColumn id="4" xr3:uid="{D8E59C8C-E121-4382-B4A3-C2F0434AC22C}" name="year" dataDxfId="0">
+    <tableColumn id="3" xr3:uid="{329E54A5-7737-4A43-B69F-B74CF0504FAA}" name="type_index"/>
+    <tableColumn id="4" xr3:uid="{D8E59C8C-E121-4382-B4A3-C2F0434AC22C}" name="year" dataDxfId="2">
       <calculatedColumnFormula>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{1A99A2C0-C670-4BC4-A5EE-F6D8691B009D}" name="authors"/>
@@ -1655,7 +2323,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{7C672562-8A52-436F-90D4-450D4B76A1EF}" name="_01_학회지논문" displayName="_01_학회지논문" ref="A1:A135" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:A135" xr:uid="{7C672562-8A52-436F-90D4-450D4B76A1EF}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{3F892609-5DEB-4271-801A-5DDD50A14F75}" uniqueName="1" name="Name" queryTableFieldId="1" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{3F892609-5DEB-4271-801A-5DDD50A14F75}" uniqueName="1" name="Name" queryTableFieldId="1" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1983,6 +2651,7 @@
   <cols>
     <col min="3" max="3" width="12.125" customWidth="1"/>
     <col min="5" max="5" width="9.5" customWidth="1"/>
+    <col min="7" max="7" width="43.25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.25" customWidth="1"/>
     <col min="10" max="10" width="9.875" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="9" customWidth="1"/>
@@ -1999,73 +2668,73 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>603</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C2" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D2">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>1996</v>
       </c>
       <c r="E2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F2" t="s">
         <v>298</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>299</v>
-      </c>
-      <c r="G2" t="s">
-        <v>300</v>
       </c>
       <c r="H2">
         <v>31</v>
@@ -2074,40 +2743,40 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="M2" t="s">
-        <v>435</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>18</v>
+        <v>434</v>
+      </c>
+      <c r="O2" t="s">
+        <v>17</v>
       </c>
       <c r="P2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C3" t="s">
-        <v>287</v>
+        <v>601</v>
       </c>
       <c r="D3">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>1996</v>
       </c>
       <c r="E3" t="s">
+        <v>301</v>
+      </c>
+      <c r="F3" t="s">
         <v>302</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>303</v>
-      </c>
-      <c r="G3" t="s">
-        <v>304</v>
       </c>
       <c r="H3">
         <v>31</v>
@@ -2116,40 +2785,40 @@
         <v>29</v>
       </c>
       <c r="J3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="M3" t="s">
-        <v>435</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>19</v>
+        <v>434</v>
+      </c>
+      <c r="O3" t="s">
+        <v>18</v>
       </c>
       <c r="P3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C4" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D4">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2001</v>
       </c>
       <c r="E4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H4">
         <v>36</v>
@@ -2158,37 +2827,37 @@
         <v>4</v>
       </c>
       <c r="M4" t="s">
-        <v>435</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>20</v>
+        <v>434</v>
+      </c>
+      <c r="O4" t="s">
+        <v>19</v>
       </c>
       <c r="P4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C5" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D5">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2002</v>
       </c>
       <c r="E5" t="s">
+        <v>306</v>
+      </c>
+      <c r="F5" t="s">
         <v>307</v>
       </c>
-      <c r="F5" t="s">
-        <v>308</v>
-      </c>
       <c r="G5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H5">
         <v>37</v>
@@ -2197,40 +2866,40 @@
         <v>5</v>
       </c>
       <c r="J5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M5" t="s">
-        <v>435</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>21</v>
+        <v>434</v>
+      </c>
+      <c r="O5" t="s">
+        <v>20</v>
       </c>
       <c r="P5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C6" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D6">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2002</v>
       </c>
       <c r="E6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H6">
         <v>37</v>
@@ -2239,40 +2908,40 @@
         <v>5</v>
       </c>
       <c r="J6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="M6" t="s">
-        <v>435</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>22</v>
+        <v>434</v>
+      </c>
+      <c r="O6" t="s">
+        <v>21</v>
       </c>
       <c r="P6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C7" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D7">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2004</v>
       </c>
       <c r="E7" t="s">
+        <v>311</v>
+      </c>
+      <c r="F7" t="s">
         <v>312</v>
       </c>
-      <c r="F7" t="s">
-        <v>313</v>
-      </c>
       <c r="G7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H7">
         <v>39</v>
@@ -2281,73 +2950,73 @@
         <v>6</v>
       </c>
       <c r="J7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M7" t="s">
-        <v>435</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>23</v>
+        <v>434</v>
+      </c>
+      <c r="O7" t="s">
+        <v>22</v>
       </c>
       <c r="P7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C8" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D8">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2004</v>
       </c>
       <c r="E8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="M8" t="s">
-        <v>288</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>24</v>
+        <v>287</v>
+      </c>
+      <c r="O8" t="s">
+        <v>23</v>
       </c>
       <c r="P8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C9" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D9">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2004</v>
       </c>
       <c r="E9" t="s">
+        <v>315</v>
+      </c>
+      <c r="F9" t="s">
         <v>316</v>
       </c>
-      <c r="F9" t="s">
-        <v>317</v>
-      </c>
       <c r="G9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H9">
         <v>39</v>
@@ -2356,97 +3025,97 @@
         <v>4</v>
       </c>
       <c r="J9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="M9" t="s">
-        <v>435</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>25</v>
+        <v>434</v>
+      </c>
+      <c r="O9" t="s">
+        <v>24</v>
       </c>
       <c r="P9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B10" t="s">
+        <v>285</v>
+      </c>
+      <c r="C10" t="s">
         <v>286</v>
       </c>
-      <c r="C10" t="s">
-        <v>287</v>
-      </c>
       <c r="D10">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2004</v>
       </c>
       <c r="M10" t="s">
-        <v>288</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>26</v>
+        <v>287</v>
+      </c>
+      <c r="O10" t="s">
+        <v>25</v>
       </c>
       <c r="P10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B11" t="s">
+        <v>285</v>
+      </c>
+      <c r="C11" t="s">
         <v>286</v>
       </c>
-      <c r="C11" t="s">
-        <v>287</v>
-      </c>
       <c r="D11">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2004</v>
       </c>
       <c r="M11" t="s">
-        <v>288</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>27</v>
+        <v>287</v>
+      </c>
+      <c r="O11" t="s">
+        <v>26</v>
       </c>
       <c r="P11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B12" t="s">
-        <v>286</v>
+        <v>602</v>
       </c>
       <c r="C12" t="s">
-        <v>287</v>
+        <v>601</v>
       </c>
       <c r="D12">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2004</v>
       </c>
       <c r="E12" t="s">
+        <v>318</v>
+      </c>
+      <c r="F12" t="s">
         <v>319</v>
       </c>
-      <c r="F12" t="s">
-        <v>320</v>
-      </c>
       <c r="G12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H12">
         <v>39</v>
@@ -2455,73 +3124,73 @@
         <v>6</v>
       </c>
       <c r="M12" t="s">
-        <v>435</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>28</v>
+        <v>434</v>
+      </c>
+      <c r="O12" t="s">
+        <v>27</v>
       </c>
       <c r="P12" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C13" t="s">
-        <v>287</v>
+        <v>601</v>
       </c>
       <c r="D13">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2005</v>
       </c>
       <c r="E13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F13" t="s">
+        <v>320</v>
+      </c>
+      <c r="G13" t="s">
         <v>321</v>
-      </c>
-      <c r="G13" t="s">
-        <v>322</v>
       </c>
       <c r="H13">
         <v>289</v>
       </c>
       <c r="M13" t="s">
-        <v>435</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>29</v>
+        <v>434</v>
+      </c>
+      <c r="O13" t="s">
+        <v>28</v>
       </c>
       <c r="P13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C14" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D14">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2005</v>
       </c>
       <c r="E14" t="s">
+        <v>322</v>
+      </c>
+      <c r="F14" t="s">
         <v>323</v>
       </c>
-      <c r="F14" t="s">
-        <v>324</v>
-      </c>
       <c r="G14" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H14">
         <v>40</v>
@@ -2530,106 +3199,106 @@
         <v>7</v>
       </c>
       <c r="J14" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="M14" t="s">
-        <v>435</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>30</v>
+        <v>434</v>
+      </c>
+      <c r="O14" t="s">
+        <v>29</v>
       </c>
       <c r="P14" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s">
+        <v>285</v>
+      </c>
+      <c r="C15" t="s">
         <v>286</v>
       </c>
-      <c r="C15" t="s">
-        <v>287</v>
-      </c>
       <c r="D15">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2005</v>
       </c>
       <c r="M15" t="s">
-        <v>288</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>31</v>
+        <v>287</v>
+      </c>
+      <c r="O15" t="s">
+        <v>30</v>
       </c>
       <c r="P15" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B16" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C16" t="s">
-        <v>287</v>
+        <v>601</v>
       </c>
       <c r="D16">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2005</v>
       </c>
       <c r="E16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F16" t="s">
+        <v>325</v>
+      </c>
+      <c r="G16" t="s">
         <v>326</v>
       </c>
-      <c r="G16" t="s">
+      <c r="J16" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="J16" s="2" t="s">
-        <v>328</v>
-      </c>
       <c r="M16" t="s">
-        <v>435</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>32</v>
+        <v>434</v>
+      </c>
+      <c r="O16" t="s">
+        <v>31</v>
       </c>
       <c r="P16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C17" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D17">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2006</v>
       </c>
       <c r="E17" t="s">
+        <v>328</v>
+      </c>
+      <c r="F17" t="s">
         <v>329</v>
       </c>
-      <c r="F17" t="s">
-        <v>330</v>
-      </c>
       <c r="G17" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H17">
         <v>41</v>
@@ -2638,40 +3307,40 @@
         <v>3</v>
       </c>
       <c r="J17" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M17" t="s">
-        <v>435</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>33</v>
+        <v>434</v>
+      </c>
+      <c r="O17" t="s">
+        <v>32</v>
       </c>
       <c r="P17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B18" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C18" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D18">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2006</v>
       </c>
       <c r="E18" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F18" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G18" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H18">
         <v>41</v>
@@ -2680,70 +3349,70 @@
         <v>7</v>
       </c>
       <c r="J18" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="M18" t="s">
-        <v>435</v>
-      </c>
-      <c r="O18" s="1" t="s">
-        <v>34</v>
+        <v>434</v>
+      </c>
+      <c r="O18" t="s">
+        <v>33</v>
       </c>
       <c r="P18" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q18" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B19" t="s">
+        <v>285</v>
+      </c>
+      <c r="C19" t="s">
         <v>286</v>
       </c>
-      <c r="C19" t="s">
-        <v>287</v>
-      </c>
       <c r="D19">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2006</v>
       </c>
       <c r="M19" t="s">
-        <v>288</v>
-      </c>
-      <c r="O19" s="1" t="s">
-        <v>35</v>
+        <v>287</v>
+      </c>
+      <c r="O19" t="s">
+        <v>34</v>
       </c>
       <c r="P19" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q19" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C20" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D20">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2006</v>
       </c>
       <c r="E20" t="s">
+        <v>333</v>
+      </c>
+      <c r="F20" t="s">
         <v>334</v>
       </c>
-      <c r="F20" t="s">
-        <v>335</v>
-      </c>
       <c r="G20" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H20">
         <v>41</v>
@@ -2752,40 +3421,40 @@
         <v>3</v>
       </c>
       <c r="J20" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="M20" t="s">
-        <v>435</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>36</v>
+        <v>434</v>
+      </c>
+      <c r="O20" t="s">
+        <v>35</v>
       </c>
       <c r="P20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B21" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C21" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D21">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2007</v>
       </c>
       <c r="E21" t="s">
+        <v>336</v>
+      </c>
+      <c r="F21" t="s">
         <v>337</v>
       </c>
-      <c r="F21" t="s">
-        <v>338</v>
-      </c>
       <c r="G21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H21">
         <v>42</v>
@@ -2794,40 +3463,40 @@
         <v>3</v>
       </c>
       <c r="J21" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M21" t="s">
-        <v>435</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>37</v>
+        <v>434</v>
+      </c>
+      <c r="O21" t="s">
+        <v>36</v>
       </c>
       <c r="P21" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B22" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C22" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D22">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2007</v>
       </c>
       <c r="E22" t="s">
+        <v>339</v>
+      </c>
+      <c r="F22" t="s">
         <v>340</v>
       </c>
-      <c r="F22" t="s">
-        <v>341</v>
-      </c>
       <c r="G22" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H22">
         <v>42</v>
@@ -2836,163 +3505,181 @@
         <v>7</v>
       </c>
       <c r="M22" t="s">
-        <v>435</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>38</v>
+        <v>434</v>
+      </c>
+      <c r="O22" t="s">
+        <v>37</v>
       </c>
       <c r="P22" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B23" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C23" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D23">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2008</v>
       </c>
       <c r="E23" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F23" t="s">
-        <v>342</v>
+        <v>341</v>
+      </c>
+      <c r="G23" t="s">
+        <v>299</v>
+      </c>
+      <c r="H23">
+        <v>43</v>
+      </c>
+      <c r="I23">
+        <v>3</v>
       </c>
       <c r="M23" t="s">
-        <v>435</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>39</v>
+        <v>434</v>
+      </c>
+      <c r="O23" t="s">
+        <v>38</v>
       </c>
       <c r="P23" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B24" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C24" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D24">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2008</v>
       </c>
       <c r="E24" t="s">
+        <v>342</v>
+      </c>
+      <c r="F24" t="s">
         <v>343</v>
       </c>
-      <c r="F24" t="s">
-        <v>344</v>
+      <c r="G24" t="s">
+        <v>299</v>
+      </c>
+      <c r="H24">
+        <v>43</v>
+      </c>
+      <c r="I24">
+        <v>3</v>
       </c>
       <c r="M24" t="s">
-        <v>435</v>
-      </c>
-      <c r="O24" s="1" t="s">
-        <v>40</v>
+        <v>434</v>
+      </c>
+      <c r="O24" t="s">
+        <v>39</v>
       </c>
       <c r="P24" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B25" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C25" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D25">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2008</v>
       </c>
       <c r="E25" t="s">
+        <v>344</v>
+      </c>
+      <c r="F25" t="s">
         <v>345</v>
       </c>
-      <c r="F25" t="s">
-        <v>346</v>
-      </c>
       <c r="G25" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H25">
         <v>43</v>
       </c>
       <c r="M25" t="s">
-        <v>435</v>
-      </c>
-      <c r="O25" s="1" t="s">
-        <v>41</v>
+        <v>434</v>
+      </c>
+      <c r="O25" t="s">
+        <v>40</v>
       </c>
       <c r="P25" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q25" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B26" t="s">
+        <v>285</v>
+      </c>
+      <c r="C26" t="s">
         <v>286</v>
       </c>
-      <c r="C26" t="s">
-        <v>287</v>
-      </c>
       <c r="D26">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2008</v>
       </c>
       <c r="M26" t="s">
-        <v>288</v>
-      </c>
-      <c r="O26" s="1" t="s">
-        <v>42</v>
+        <v>287</v>
+      </c>
+      <c r="O26" t="s">
+        <v>41</v>
       </c>
       <c r="P26" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q26" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C27" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D27">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2009</v>
       </c>
       <c r="E27" t="s">
+        <v>346</v>
+      </c>
+      <c r="F27" t="s">
         <v>347</v>
       </c>
-      <c r="F27" t="s">
-        <v>348</v>
-      </c>
       <c r="G27" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H27">
         <v>44</v>
@@ -3001,70 +3688,70 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M27" t="s">
-        <v>435</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>43</v>
+        <v>434</v>
+      </c>
+      <c r="O27" t="s">
+        <v>42</v>
       </c>
       <c r="P27" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q27" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B28" t="s">
+        <v>285</v>
+      </c>
+      <c r="C28" t="s">
         <v>286</v>
       </c>
-      <c r="C28" t="s">
-        <v>287</v>
-      </c>
       <c r="D28">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2009</v>
       </c>
       <c r="M28" t="s">
-        <v>288</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>44</v>
+        <v>287</v>
+      </c>
+      <c r="O28" t="s">
+        <v>43</v>
       </c>
       <c r="P28" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q28" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B29" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C29" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D29">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2009</v>
       </c>
       <c r="E29" t="s">
+        <v>349</v>
+      </c>
+      <c r="F29" t="s">
         <v>350</v>
       </c>
-      <c r="F29" t="s">
-        <v>351</v>
-      </c>
       <c r="G29" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H29">
         <v>44</v>
@@ -3073,37 +3760,40 @@
         <v>5</v>
       </c>
       <c r="J29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M29" t="s">
-        <v>435</v>
-      </c>
-      <c r="O29" s="1" t="s">
-        <v>45</v>
+        <v>434</v>
+      </c>
+      <c r="O29" t="s">
+        <v>44</v>
       </c>
       <c r="P29" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B30" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C30" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D30">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2009</v>
       </c>
       <c r="E30" t="s">
+        <v>352</v>
+      </c>
+      <c r="F30" t="s">
         <v>353</v>
       </c>
-      <c r="F30" t="s">
-        <v>354</v>
+      <c r="G30" t="s">
+        <v>299</v>
       </c>
       <c r="H30">
         <v>44</v>
@@ -3112,70 +3802,70 @@
         <v>3</v>
       </c>
       <c r="J30" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="M30" t="s">
-        <v>435</v>
-      </c>
-      <c r="O30" s="1" t="s">
-        <v>46</v>
+        <v>434</v>
+      </c>
+      <c r="O30" t="s">
+        <v>45</v>
       </c>
       <c r="P30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q30" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B31" t="s">
+        <v>285</v>
+      </c>
+      <c r="C31" t="s">
         <v>286</v>
       </c>
-      <c r="C31" t="s">
-        <v>287</v>
-      </c>
       <c r="D31">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2009</v>
       </c>
       <c r="M31" t="s">
-        <v>288</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>47</v>
+        <v>287</v>
+      </c>
+      <c r="O31" t="s">
+        <v>46</v>
       </c>
       <c r="P31" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q31" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B32" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C32" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D32">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2010</v>
       </c>
       <c r="E32" t="s">
+        <v>355</v>
+      </c>
+      <c r="F32" t="s">
         <v>356</v>
       </c>
-      <c r="F32" t="s">
-        <v>357</v>
-      </c>
       <c r="G32" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H32">
         <v>45</v>
@@ -3184,40 +3874,40 @@
         <v>7</v>
       </c>
       <c r="J32" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="M32" t="s">
-        <v>435</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>48</v>
+        <v>434</v>
+      </c>
+      <c r="O32" t="s">
+        <v>47</v>
       </c>
       <c r="P32" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B33" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C33" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D33">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2010</v>
       </c>
       <c r="E33" t="s">
+        <v>358</v>
+      </c>
+      <c r="F33" t="s">
         <v>359</v>
       </c>
-      <c r="F33" t="s">
-        <v>360</v>
-      </c>
       <c r="G33" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H33">
         <v>45</v>
@@ -3226,40 +3916,40 @@
         <v>2</v>
       </c>
       <c r="J33" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="M33" t="s">
-        <v>435</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>49</v>
+        <v>434</v>
+      </c>
+      <c r="O33" t="s">
+        <v>48</v>
       </c>
       <c r="P33" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B34" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C34" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D34">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2010</v>
       </c>
       <c r="E34" t="s">
+        <v>361</v>
+      </c>
+      <c r="F34" t="s">
         <v>362</v>
       </c>
-      <c r="F34" t="s">
-        <v>363</v>
-      </c>
       <c r="G34" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H34">
         <v>45</v>
@@ -3268,40 +3958,40 @@
         <v>4</v>
       </c>
       <c r="J34" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="M34" t="s">
-        <v>435</v>
-      </c>
-      <c r="O34" s="1" t="s">
-        <v>50</v>
+        <v>434</v>
+      </c>
+      <c r="O34" t="s">
+        <v>49</v>
       </c>
       <c r="P34" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B35" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C35" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D35">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2010</v>
       </c>
       <c r="E35" t="s">
+        <v>364</v>
+      </c>
+      <c r="F35" t="s">
         <v>365</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>366</v>
-      </c>
-      <c r="G35" t="s">
-        <v>367</v>
       </c>
       <c r="H35">
         <v>23</v>
@@ -3310,40 +4000,40 @@
         <v>3</v>
       </c>
       <c r="J35" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="M35" t="s">
-        <v>435</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>51</v>
+        <v>434</v>
+      </c>
+      <c r="O35" t="s">
+        <v>50</v>
       </c>
       <c r="P35" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B36" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C36" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D36">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2011</v>
       </c>
       <c r="E36" t="s">
+        <v>368</v>
+      </c>
+      <c r="F36" t="s">
         <v>369</v>
       </c>
-      <c r="F36" t="s">
-        <v>370</v>
-      </c>
       <c r="G36" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H36">
         <v>46</v>
@@ -3352,37 +4042,37 @@
         <v>3</v>
       </c>
       <c r="M36" t="s">
-        <v>435</v>
-      </c>
-      <c r="O36" s="1" t="s">
-        <v>52</v>
+        <v>434</v>
+      </c>
+      <c r="O36" t="s">
+        <v>51</v>
       </c>
       <c r="P36" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B37" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C37" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D37">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2011</v>
       </c>
       <c r="E37" t="s">
+        <v>370</v>
+      </c>
+      <c r="F37" t="s">
         <v>371</v>
       </c>
-      <c r="F37" t="s">
-        <v>372</v>
-      </c>
       <c r="G37" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H37">
         <v>46</v>
@@ -3391,70 +4081,79 @@
         <v>4</v>
       </c>
       <c r="J37" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M37" t="s">
-        <v>435</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>53</v>
+        <v>434</v>
+      </c>
+      <c r="O37" t="s">
+        <v>52</v>
       </c>
       <c r="P37" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B38" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C38" t="s">
-        <v>287</v>
+        <v>601</v>
       </c>
       <c r="D38">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2011</v>
       </c>
       <c r="E38" t="s">
+        <v>373</v>
+      </c>
+      <c r="F38" t="s">
         <v>374</v>
       </c>
-      <c r="F38" t="s">
-        <v>375</v>
+      <c r="G38" t="s">
+        <v>380</v>
+      </c>
+      <c r="H38">
+        <v>12</v>
+      </c>
+      <c r="I38">
+        <v>4</v>
       </c>
       <c r="M38" t="s">
-        <v>435</v>
-      </c>
-      <c r="O38" s="1" t="s">
-        <v>54</v>
+        <v>434</v>
+      </c>
+      <c r="O38" t="s">
+        <v>53</v>
       </c>
       <c r="P38" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B39" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C39" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D39">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2012</v>
       </c>
       <c r="E39" t="s">
+        <v>375</v>
+      </c>
+      <c r="F39" t="s">
         <v>376</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>377</v>
-      </c>
-      <c r="G39" t="s">
-        <v>378</v>
       </c>
       <c r="H39">
         <v>28</v>
@@ -3463,37 +4162,37 @@
         <v>2</v>
       </c>
       <c r="M39" t="s">
-        <v>435</v>
-      </c>
-      <c r="O39" s="1" t="s">
-        <v>55</v>
+        <v>434</v>
+      </c>
+      <c r="O39" t="s">
+        <v>54</v>
       </c>
       <c r="P39" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B40" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C40" t="s">
-        <v>287</v>
+        <v>601</v>
       </c>
       <c r="D40">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2012</v>
       </c>
       <c r="E40" t="s">
+        <v>378</v>
+      </c>
+      <c r="F40" t="s">
         <v>379</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>380</v>
-      </c>
-      <c r="G40" t="s">
-        <v>381</v>
       </c>
       <c r="H40">
         <v>13</v>
@@ -3502,37 +4201,37 @@
         <v>2</v>
       </c>
       <c r="M40" t="s">
-        <v>435</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>56</v>
+        <v>434</v>
+      </c>
+      <c r="O40" t="s">
+        <v>55</v>
       </c>
       <c r="P40" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B41" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C41" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D41">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2012</v>
       </c>
       <c r="E41" t="s">
+        <v>381</v>
+      </c>
+      <c r="F41" t="s">
         <v>382</v>
       </c>
-      <c r="F41" t="s">
-        <v>383</v>
-      </c>
       <c r="G41" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H41">
         <v>28</v>
@@ -3541,37 +4240,37 @@
         <v>4</v>
       </c>
       <c r="M41" t="s">
-        <v>435</v>
-      </c>
-      <c r="O41" s="1" t="s">
-        <v>57</v>
+        <v>434</v>
+      </c>
+      <c r="O41" t="s">
+        <v>56</v>
       </c>
       <c r="P41" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B42" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C42" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D42">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2012</v>
       </c>
       <c r="E42" t="s">
+        <v>383</v>
+      </c>
+      <c r="F42" t="s">
         <v>384</v>
       </c>
-      <c r="F42" t="s">
-        <v>385</v>
-      </c>
       <c r="G42" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H42">
         <v>47</v>
@@ -3580,37 +4279,37 @@
         <v>4</v>
       </c>
       <c r="M42" t="s">
-        <v>435</v>
-      </c>
-      <c r="O42" s="1" t="s">
-        <v>58</v>
+        <v>434</v>
+      </c>
+      <c r="O42" t="s">
+        <v>57</v>
       </c>
       <c r="P42" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B43" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C43" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D43">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2012</v>
       </c>
       <c r="E43" t="s">
+        <v>385</v>
+      </c>
+      <c r="F43" t="s">
         <v>386</v>
       </c>
-      <c r="F43" t="s">
-        <v>387</v>
-      </c>
       <c r="G43" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H43">
         <v>47</v>
@@ -3619,37 +4318,37 @@
         <v>5</v>
       </c>
       <c r="M43" t="s">
-        <v>435</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>59</v>
+        <v>434</v>
+      </c>
+      <c r="O43" t="s">
+        <v>58</v>
       </c>
       <c r="P43" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B44" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C44" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D44">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2012</v>
       </c>
       <c r="E44" t="s">
+        <v>387</v>
+      </c>
+      <c r="F44" t="s">
         <v>388</v>
       </c>
-      <c r="F44" t="s">
-        <v>389</v>
-      </c>
       <c r="G44" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H44">
         <v>47</v>
@@ -3658,37 +4357,37 @@
         <v>2</v>
       </c>
       <c r="M44" t="s">
-        <v>435</v>
-      </c>
-      <c r="O44" s="1" t="s">
-        <v>60</v>
+        <v>434</v>
+      </c>
+      <c r="O44" t="s">
+        <v>59</v>
       </c>
       <c r="P44" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B45" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C45" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D45">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2012</v>
       </c>
       <c r="E45" t="s">
+        <v>389</v>
+      </c>
+      <c r="F45" t="s">
         <v>390</v>
       </c>
-      <c r="F45" t="s">
-        <v>391</v>
-      </c>
       <c r="G45" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H45">
         <v>47</v>
@@ -3697,37 +4396,37 @@
         <v>7</v>
       </c>
       <c r="M45" t="s">
-        <v>435</v>
-      </c>
-      <c r="O45" s="1" t="s">
-        <v>61</v>
+        <v>434</v>
+      </c>
+      <c r="O45" t="s">
+        <v>60</v>
       </c>
       <c r="P45" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B46" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C46" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D46">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2012</v>
       </c>
       <c r="E46" t="s">
+        <v>391</v>
+      </c>
+      <c r="F46" t="s">
         <v>392</v>
       </c>
-      <c r="F46" t="s">
-        <v>393</v>
-      </c>
       <c r="G46" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H46">
         <v>47</v>
@@ -3736,37 +4435,37 @@
         <v>1</v>
       </c>
       <c r="M46" t="s">
-        <v>435</v>
-      </c>
-      <c r="O46" s="1" t="s">
-        <v>62</v>
+        <v>434</v>
+      </c>
+      <c r="O46" t="s">
+        <v>61</v>
       </c>
       <c r="P46" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C47" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D47">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2013</v>
       </c>
       <c r="E47" t="s">
+        <v>393</v>
+      </c>
+      <c r="F47" t="s">
         <v>394</v>
       </c>
-      <c r="F47" t="s">
-        <v>395</v>
-      </c>
       <c r="G47" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H47">
         <v>48</v>
@@ -3775,37 +4474,37 @@
         <v>1</v>
       </c>
       <c r="M47" t="s">
-        <v>435</v>
-      </c>
-      <c r="O47" s="1" t="s">
-        <v>63</v>
+        <v>434</v>
+      </c>
+      <c r="O47" t="s">
+        <v>62</v>
       </c>
       <c r="P47" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B48" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C48" t="s">
-        <v>287</v>
+        <v>601</v>
       </c>
       <c r="D48">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2013</v>
       </c>
       <c r="E48" t="s">
+        <v>395</v>
+      </c>
+      <c r="F48" t="s">
         <v>396</v>
       </c>
-      <c r="F48" t="s">
-        <v>397</v>
-      </c>
       <c r="G48" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H48">
         <v>14</v>
@@ -3814,37 +4513,37 @@
         <v>1</v>
       </c>
       <c r="M48" t="s">
-        <v>435</v>
-      </c>
-      <c r="O48" s="1" t="s">
-        <v>64</v>
+        <v>434</v>
+      </c>
+      <c r="O48" t="s">
+        <v>63</v>
       </c>
       <c r="P48" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B49" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C49" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D49">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2013</v>
       </c>
       <c r="E49" t="s">
+        <v>397</v>
+      </c>
+      <c r="F49" t="s">
         <v>398</v>
       </c>
-      <c r="F49" t="s">
-        <v>399</v>
-      </c>
       <c r="G49" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H49">
         <v>48</v>
@@ -3853,37 +4552,37 @@
         <v>5</v>
       </c>
       <c r="M49" t="s">
-        <v>435</v>
-      </c>
-      <c r="O49" s="1" t="s">
-        <v>65</v>
+        <v>434</v>
+      </c>
+      <c r="O49" t="s">
+        <v>64</v>
       </c>
       <c r="P49" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B50" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C50" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D50">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2013</v>
       </c>
       <c r="E50" t="s">
+        <v>399</v>
+      </c>
+      <c r="F50" t="s">
         <v>400</v>
       </c>
-      <c r="F50" t="s">
-        <v>401</v>
-      </c>
       <c r="G50" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H50">
         <v>48</v>
@@ -3892,37 +4591,37 @@
         <v>5</v>
       </c>
       <c r="M50" t="s">
-        <v>435</v>
-      </c>
-      <c r="O50" s="1" t="s">
-        <v>66</v>
+        <v>434</v>
+      </c>
+      <c r="O50" t="s">
+        <v>65</v>
       </c>
       <c r="P50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C51" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D51">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2013</v>
       </c>
       <c r="E51" t="s">
+        <v>401</v>
+      </c>
+      <c r="F51" t="s">
         <v>402</v>
       </c>
-      <c r="F51" t="s">
-        <v>403</v>
-      </c>
       <c r="G51" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H51">
         <v>48</v>
@@ -3931,37 +4630,37 @@
         <v>3</v>
       </c>
       <c r="M51" t="s">
-        <v>435</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>67</v>
+        <v>434</v>
+      </c>
+      <c r="O51" t="s">
+        <v>66</v>
       </c>
       <c r="P51" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C52" t="s">
-        <v>287</v>
+        <v>601</v>
       </c>
       <c r="D52">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2013</v>
       </c>
       <c r="E52" t="s">
+        <v>403</v>
+      </c>
+      <c r="F52" t="s">
         <v>404</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>405</v>
-      </c>
-      <c r="G52" t="s">
-        <v>406</v>
       </c>
       <c r="H52">
         <v>14</v>
@@ -3970,37 +4669,37 @@
         <v>4</v>
       </c>
       <c r="M52" t="s">
-        <v>435</v>
-      </c>
-      <c r="O52" s="1" t="s">
-        <v>68</v>
+        <v>434</v>
+      </c>
+      <c r="O52" t="s">
+        <v>67</v>
       </c>
       <c r="P52" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C53" t="s">
-        <v>287</v>
+        <v>601</v>
       </c>
       <c r="D53">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2014</v>
       </c>
       <c r="E53" t="s">
+        <v>406</v>
+      </c>
+      <c r="F53" t="s">
         <v>407</v>
       </c>
-      <c r="F53" t="s">
-        <v>408</v>
-      </c>
       <c r="G53" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H53">
         <v>15</v>
@@ -4009,37 +4708,37 @@
         <v>3</v>
       </c>
       <c r="M53" t="s">
-        <v>435</v>
-      </c>
-      <c r="O53" s="1" t="s">
-        <v>69</v>
+        <v>434</v>
+      </c>
+      <c r="O53" t="s">
+        <v>68</v>
       </c>
       <c r="P53" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B54" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C54" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D54">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2014</v>
       </c>
       <c r="E54" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F54" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G54" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H54">
         <v>49</v>
@@ -4048,37 +4747,37 @@
         <v>7</v>
       </c>
       <c r="M54" t="s">
-        <v>435</v>
-      </c>
-      <c r="O54" s="1" t="s">
-        <v>70</v>
+        <v>434</v>
+      </c>
+      <c r="O54" t="s">
+        <v>69</v>
       </c>
       <c r="P54" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B55" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C55" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D55">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2014</v>
       </c>
       <c r="E55" t="s">
+        <v>409</v>
+      </c>
+      <c r="F55" t="s">
         <v>410</v>
       </c>
-      <c r="F55" t="s">
-        <v>411</v>
-      </c>
       <c r="G55" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H55">
         <v>49</v>
@@ -4087,37 +4786,37 @@
         <v>8</v>
       </c>
       <c r="M55" t="s">
-        <v>435</v>
-      </c>
-      <c r="O55" s="1" t="s">
-        <v>71</v>
+        <v>434</v>
+      </c>
+      <c r="O55" t="s">
+        <v>70</v>
       </c>
       <c r="P55" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B56" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C56" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D56">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2015</v>
       </c>
       <c r="E56" t="s">
+        <v>411</v>
+      </c>
+      <c r="F56" t="s">
         <v>412</v>
       </c>
-      <c r="F56" t="s">
-        <v>413</v>
-      </c>
       <c r="G56" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H56">
         <v>50</v>
@@ -4126,37 +4825,37 @@
         <v>2</v>
       </c>
       <c r="M56" t="s">
-        <v>435</v>
-      </c>
-      <c r="O56" s="1" t="s">
-        <v>72</v>
+        <v>434</v>
+      </c>
+      <c r="O56" t="s">
+        <v>71</v>
       </c>
       <c r="P56" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B57" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C57" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D57">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2015</v>
       </c>
       <c r="E57" t="s">
+        <v>413</v>
+      </c>
+      <c r="F57" t="s">
         <v>414</v>
       </c>
-      <c r="F57" t="s">
-        <v>415</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>300</v>
+      <c r="G57" s="2" t="s">
+        <v>299</v>
       </c>
       <c r="H57">
         <v>50</v>
@@ -4165,37 +4864,37 @@
         <v>5</v>
       </c>
       <c r="M57" t="s">
-        <v>435</v>
-      </c>
-      <c r="O57" s="1" t="s">
-        <v>73</v>
+        <v>434</v>
+      </c>
+      <c r="O57" t="s">
+        <v>72</v>
       </c>
       <c r="P57" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B58" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C58" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D58">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2015</v>
       </c>
       <c r="E58" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F58" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G58" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H58">
         <v>28</v>
@@ -4204,37 +4903,37 @@
         <v>2</v>
       </c>
       <c r="M58" t="s">
-        <v>435</v>
-      </c>
-      <c r="O58" s="1" t="s">
-        <v>74</v>
+        <v>434</v>
+      </c>
+      <c r="O58" t="s">
+        <v>73</v>
       </c>
       <c r="P58" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B59" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C59" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D59">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2015</v>
       </c>
       <c r="E59" t="s">
+        <v>416</v>
+      </c>
+      <c r="F59" t="s">
         <v>417</v>
       </c>
-      <c r="F59" t="s">
-        <v>418</v>
-      </c>
       <c r="G59" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H59">
         <v>50</v>
@@ -4243,37 +4942,37 @@
         <v>3</v>
       </c>
       <c r="M59" t="s">
-        <v>435</v>
-      </c>
-      <c r="O59" s="1" t="s">
-        <v>75</v>
+        <v>434</v>
+      </c>
+      <c r="O59" t="s">
+        <v>74</v>
       </c>
       <c r="P59" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B60" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C60" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D60">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2015</v>
       </c>
       <c r="E60" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F60" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G60" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H60">
         <v>50</v>
@@ -4282,37 +4981,37 @@
         <v>8</v>
       </c>
       <c r="M60" t="s">
-        <v>435</v>
-      </c>
-      <c r="O60" s="1" t="s">
-        <v>76</v>
+        <v>434</v>
+      </c>
+      <c r="O60" t="s">
+        <v>75</v>
       </c>
       <c r="P60" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B61" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C61" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D61">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2015</v>
       </c>
       <c r="E61" t="s">
+        <v>419</v>
+      </c>
+      <c r="F61" t="s">
         <v>420</v>
       </c>
-      <c r="F61" t="s">
-        <v>421</v>
-      </c>
       <c r="G61" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H61">
         <v>50</v>
@@ -4321,73 +5020,73 @@
         <v>3</v>
       </c>
       <c r="M61" t="s">
-        <v>435</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>77</v>
+        <v>434</v>
+      </c>
+      <c r="O61" t="s">
+        <v>76</v>
       </c>
       <c r="P61" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B62" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C62" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D62">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2015</v>
       </c>
       <c r="E62" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F62" t="s">
+        <v>421</v>
+      </c>
+      <c r="G62" t="s">
         <v>422</v>
-      </c>
-      <c r="G62" t="s">
-        <v>423</v>
       </c>
       <c r="H62">
         <v>63</v>
       </c>
       <c r="M62" t="s">
-        <v>435</v>
-      </c>
-      <c r="O62" s="1" t="s">
-        <v>78</v>
+        <v>434</v>
+      </c>
+      <c r="O62" t="s">
+        <v>77</v>
       </c>
       <c r="P62" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B63" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C63" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D63">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2015</v>
       </c>
       <c r="E63" t="s">
+        <v>423</v>
+      </c>
+      <c r="F63" t="s">
         <v>424</v>
       </c>
-      <c r="F63" t="s">
-        <v>425</v>
-      </c>
       <c r="G63" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H63">
         <v>50</v>
@@ -4396,37 +5095,37 @@
         <v>4</v>
       </c>
       <c r="M63" t="s">
-        <v>435</v>
-      </c>
-      <c r="O63" s="1" t="s">
-        <v>79</v>
+        <v>434</v>
+      </c>
+      <c r="O63" t="s">
+        <v>78</v>
       </c>
       <c r="P63" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B64" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C64" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D64">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2016</v>
       </c>
       <c r="E64" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F64" t="s">
+        <v>425</v>
+      </c>
+      <c r="G64" t="s">
         <v>426</v>
-      </c>
-      <c r="G64" t="s">
-        <v>427</v>
       </c>
       <c r="H64">
         <v>28</v>
@@ -4435,37 +5134,37 @@
         <v>1</v>
       </c>
       <c r="M64" t="s">
-        <v>435</v>
-      </c>
-      <c r="O64" s="1" t="s">
-        <v>80</v>
+        <v>434</v>
+      </c>
+      <c r="O64" t="s">
+        <v>79</v>
       </c>
       <c r="P64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B65" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C65" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D65">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2016</v>
       </c>
       <c r="E65" t="s">
+        <v>427</v>
+      </c>
+      <c r="F65" t="s">
         <v>428</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>429</v>
-      </c>
-      <c r="G65" t="s">
-        <v>430</v>
       </c>
       <c r="H65">
         <v>17</v>
@@ -4474,37 +5173,37 @@
         <v>2</v>
       </c>
       <c r="M65" t="s">
-        <v>435</v>
-      </c>
-      <c r="O65" s="1" t="s">
-        <v>81</v>
+        <v>434</v>
+      </c>
+      <c r="O65" t="s">
+        <v>80</v>
       </c>
       <c r="P65" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B66" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C66" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D66">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2016</v>
       </c>
       <c r="E66" t="s">
+        <v>430</v>
+      </c>
+      <c r="F66" t="s">
         <v>431</v>
       </c>
-      <c r="F66" t="s">
-        <v>432</v>
-      </c>
       <c r="G66" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H66">
         <v>32</v>
@@ -4513,37 +5212,37 @@
         <v>1</v>
       </c>
       <c r="M66" t="s">
-        <v>435</v>
-      </c>
-      <c r="O66" s="1" t="s">
-        <v>82</v>
+        <v>434</v>
+      </c>
+      <c r="O66" t="s">
+        <v>81</v>
       </c>
       <c r="P66" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B67" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C67" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D67">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2016</v>
       </c>
       <c r="E67" t="s">
+        <v>432</v>
+      </c>
+      <c r="F67" t="s">
         <v>433</v>
       </c>
-      <c r="F67" t="s">
-        <v>434</v>
-      </c>
       <c r="G67" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H67">
         <v>51</v>
@@ -4552,1651 +5251,2767 @@
         <v>3</v>
       </c>
       <c r="M67" t="s">
-        <v>435</v>
-      </c>
-      <c r="O67" s="1" t="s">
-        <v>83</v>
+        <v>434</v>
+      </c>
+      <c r="O67" t="s">
+        <v>82</v>
       </c>
       <c r="P67" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B68" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C68" t="s">
-        <v>287</v>
+        <v>601</v>
       </c>
       <c r="D68">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2016</v>
       </c>
+      <c r="E68" t="s">
+        <v>435</v>
+      </c>
+      <c r="F68" t="s">
+        <v>436</v>
+      </c>
+      <c r="G68" t="s">
+        <v>380</v>
+      </c>
+      <c r="H68">
+        <v>17</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
       <c r="M68" t="s">
-        <v>288</v>
-      </c>
-      <c r="O68" s="1" t="s">
-        <v>84</v>
+        <v>434</v>
+      </c>
+      <c r="O68" t="s">
+        <v>83</v>
       </c>
       <c r="P68" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B69" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C69" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D69">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2016</v>
       </c>
+      <c r="E69" t="s">
+        <v>437</v>
+      </c>
+      <c r="F69" t="s">
+        <v>438</v>
+      </c>
+      <c r="G69" t="s">
+        <v>422</v>
+      </c>
+      <c r="H69">
+        <v>65</v>
+      </c>
       <c r="M69" t="s">
-        <v>288</v>
-      </c>
-      <c r="O69" s="1" t="s">
-        <v>85</v>
+        <v>434</v>
+      </c>
+      <c r="O69" t="s">
+        <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B70" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C70" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D70">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2016</v>
       </c>
+      <c r="E70" t="s">
+        <v>349</v>
+      </c>
+      <c r="F70" t="s">
+        <v>439</v>
+      </c>
+      <c r="G70" t="s">
+        <v>422</v>
+      </c>
+      <c r="H70">
+        <v>66</v>
+      </c>
       <c r="M70" t="s">
-        <v>288</v>
-      </c>
-      <c r="O70" s="1" t="s">
-        <v>86</v>
+        <v>434</v>
+      </c>
+      <c r="O70" t="s">
+        <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B71" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C71" t="s">
-        <v>287</v>
+        <v>601</v>
       </c>
       <c r="D71">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2016</v>
       </c>
+      <c r="E71" t="s">
+        <v>399</v>
+      </c>
+      <c r="F71" t="s">
+        <v>440</v>
+      </c>
+      <c r="G71" t="s">
+        <v>380</v>
+      </c>
+      <c r="H71">
+        <v>17</v>
+      </c>
+      <c r="I71">
+        <v>3</v>
+      </c>
       <c r="M71" t="s">
-        <v>288</v>
-      </c>
-      <c r="O71" s="1" t="s">
-        <v>87</v>
+        <v>434</v>
+      </c>
+      <c r="O71" t="s">
+        <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B72" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C72" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D72">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2016</v>
       </c>
+      <c r="E72" t="s">
+        <v>441</v>
+      </c>
+      <c r="F72" t="s">
+        <v>442</v>
+      </c>
+      <c r="G72" t="s">
+        <v>299</v>
+      </c>
+      <c r="H72">
+        <v>51</v>
+      </c>
+      <c r="I72">
+        <v>4</v>
+      </c>
       <c r="M72" t="s">
-        <v>288</v>
-      </c>
-      <c r="O72" s="1" t="s">
-        <v>88</v>
+        <v>434</v>
+      </c>
+      <c r="O72" t="s">
+        <v>87</v>
       </c>
       <c r="P72" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B73" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C73" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D73">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2016</v>
       </c>
+      <c r="E73" t="s">
+        <v>389</v>
+      </c>
+      <c r="F73" t="s">
+        <v>443</v>
+      </c>
+      <c r="G73" t="s">
+        <v>366</v>
+      </c>
+      <c r="H73">
+        <v>29</v>
+      </c>
+      <c r="I73">
+        <v>1</v>
+      </c>
       <c r="M73" t="s">
-        <v>288</v>
-      </c>
-      <c r="O73" s="1" t="s">
-        <v>89</v>
+        <v>434</v>
+      </c>
+      <c r="O73" t="s">
+        <v>88</v>
       </c>
       <c r="P73" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B74" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C74" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D74">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2016</v>
       </c>
+      <c r="E74" t="s">
+        <v>444</v>
+      </c>
+      <c r="F74" t="s">
+        <v>445</v>
+      </c>
+      <c r="G74" t="s">
+        <v>299</v>
+      </c>
+      <c r="H74">
+        <v>51</v>
+      </c>
+      <c r="I74">
+        <v>7</v>
+      </c>
       <c r="M74" t="s">
-        <v>288</v>
-      </c>
-      <c r="O74" s="1" t="s">
-        <v>90</v>
+        <v>434</v>
+      </c>
+      <c r="O74" t="s">
+        <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B75" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C75" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D75">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2017</v>
       </c>
+      <c r="E75" t="s">
+        <v>446</v>
+      </c>
+      <c r="F75" t="s">
+        <v>447</v>
+      </c>
+      <c r="G75" t="s">
+        <v>299</v>
+      </c>
+      <c r="H75">
+        <v>52</v>
+      </c>
+      <c r="I75">
+        <v>6</v>
+      </c>
       <c r="M75" t="s">
-        <v>288</v>
-      </c>
-      <c r="O75" s="1" t="s">
-        <v>91</v>
+        <v>434</v>
+      </c>
+      <c r="O75" t="s">
+        <v>90</v>
       </c>
       <c r="P75" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B76" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C76" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D76">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2017</v>
       </c>
+      <c r="E76" t="s">
+        <v>448</v>
+      </c>
+      <c r="F76" t="s">
+        <v>449</v>
+      </c>
+      <c r="G76" t="s">
+        <v>299</v>
+      </c>
+      <c r="H76">
+        <v>52</v>
+      </c>
+      <c r="I76">
+        <v>4</v>
+      </c>
       <c r="M76" t="s">
-        <v>288</v>
-      </c>
-      <c r="O76" s="1" t="s">
-        <v>92</v>
+        <v>434</v>
+      </c>
+      <c r="O76" t="s">
+        <v>91</v>
       </c>
       <c r="P76" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B77" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C77" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D77">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2017</v>
       </c>
+      <c r="E77" t="s">
+        <v>450</v>
+      </c>
+      <c r="F77" t="s">
+        <v>451</v>
+      </c>
+      <c r="G77" t="s">
+        <v>366</v>
+      </c>
+      <c r="H77">
+        <v>30</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
       <c r="M77" t="s">
-        <v>288</v>
-      </c>
-      <c r="O77" s="1" t="s">
-        <v>93</v>
+        <v>434</v>
+      </c>
+      <c r="O77" t="s">
+        <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B78" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C78" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D78">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2017</v>
       </c>
+      <c r="E78" t="s">
+        <v>452</v>
+      </c>
+      <c r="F78" t="s">
+        <v>453</v>
+      </c>
+      <c r="G78" t="s">
+        <v>299</v>
+      </c>
+      <c r="H78">
+        <v>52</v>
+      </c>
+      <c r="I78">
+        <v>1</v>
+      </c>
       <c r="M78" t="s">
-        <v>288</v>
-      </c>
-      <c r="O78" s="1" t="s">
-        <v>94</v>
+        <v>434</v>
+      </c>
+      <c r="O78" t="s">
+        <v>93</v>
       </c>
       <c r="P78" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B79" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C79" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D79">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2018</v>
       </c>
+      <c r="E79" t="s">
+        <v>454</v>
+      </c>
+      <c r="F79" t="s">
+        <v>455</v>
+      </c>
+      <c r="G79" t="s">
+        <v>299</v>
+      </c>
+      <c r="H79">
+        <v>53</v>
+      </c>
+      <c r="I79">
+        <v>2</v>
+      </c>
       <c r="M79" t="s">
-        <v>288</v>
-      </c>
-      <c r="O79" s="1" t="s">
-        <v>95</v>
+        <v>434</v>
+      </c>
+      <c r="O79" t="s">
+        <v>94</v>
       </c>
       <c r="P79" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B80" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C80" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D80">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2018</v>
       </c>
+      <c r="E80" t="s">
+        <v>349</v>
+      </c>
+      <c r="F80" t="s">
+        <v>456</v>
+      </c>
+      <c r="G80" t="s">
+        <v>457</v>
+      </c>
+      <c r="H80">
+        <v>24</v>
+      </c>
+      <c r="I80">
+        <v>2</v>
+      </c>
+      <c r="J80" t="s">
+        <v>357</v>
+      </c>
       <c r="M80" t="s">
-        <v>288</v>
-      </c>
-      <c r="O80" s="1" t="s">
-        <v>96</v>
+        <v>434</v>
+      </c>
+      <c r="O80" t="s">
+        <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B81" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C81" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D81">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2018</v>
       </c>
+      <c r="E81" t="s">
+        <v>399</v>
+      </c>
+      <c r="F81" t="s">
+        <v>458</v>
+      </c>
+      <c r="G81" t="s">
+        <v>422</v>
+      </c>
+      <c r="H81">
+        <v>73</v>
+      </c>
       <c r="M81" t="s">
-        <v>288</v>
-      </c>
-      <c r="O81" s="1" t="s">
-        <v>97</v>
+        <v>434</v>
+      </c>
+      <c r="O81" t="s">
+        <v>96</v>
       </c>
       <c r="P81" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B82" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C82" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D82">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2018</v>
       </c>
+      <c r="E82" t="s">
+        <v>459</v>
+      </c>
+      <c r="F82" t="s">
+        <v>460</v>
+      </c>
+      <c r="G82" t="s">
+        <v>299</v>
+      </c>
+      <c r="H82">
+        <v>53</v>
+      </c>
+      <c r="I82">
+        <v>6</v>
+      </c>
       <c r="M82" t="s">
-        <v>288</v>
-      </c>
-      <c r="O82" s="1" t="s">
-        <v>98</v>
+        <v>434</v>
+      </c>
+      <c r="O82" t="s">
+        <v>97</v>
       </c>
       <c r="P82" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B83" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C83" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D83">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2018</v>
       </c>
+      <c r="E83" t="s">
+        <v>461</v>
+      </c>
+      <c r="F83" t="s">
+        <v>462</v>
+      </c>
+      <c r="G83" t="s">
+        <v>463</v>
+      </c>
+      <c r="H83">
+        <v>32</v>
+      </c>
+      <c r="I83">
+        <v>6</v>
+      </c>
       <c r="M83" t="s">
-        <v>288</v>
-      </c>
-      <c r="O83" s="1" t="s">
-        <v>99</v>
+        <v>434</v>
+      </c>
+      <c r="O83" t="s">
+        <v>98</v>
       </c>
       <c r="P83" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B84" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C84" t="s">
-        <v>287</v>
+        <v>467</v>
       </c>
       <c r="D84">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2019</v>
       </c>
+      <c r="E84" t="s">
+        <v>464</v>
+      </c>
+      <c r="F84" t="s">
+        <v>465</v>
+      </c>
+      <c r="G84" t="s">
+        <v>466</v>
+      </c>
+      <c r="H84">
+        <v>50</v>
+      </c>
+      <c r="J84" t="s">
+        <v>468</v>
+      </c>
       <c r="M84" t="s">
-        <v>288</v>
-      </c>
-      <c r="O84" s="1" t="s">
-        <v>100</v>
+        <v>434</v>
+      </c>
+      <c r="O84" t="s">
+        <v>99</v>
       </c>
       <c r="P84" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B85" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C85" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D85">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2019</v>
       </c>
+      <c r="E85" t="s">
+        <v>437</v>
+      </c>
+      <c r="F85" t="s">
+        <v>469</v>
+      </c>
+      <c r="G85" t="s">
+        <v>299</v>
+      </c>
+      <c r="H85">
+        <v>54</v>
+      </c>
+      <c r="I85">
+        <v>4</v>
+      </c>
       <c r="M85" t="s">
-        <v>288</v>
-      </c>
-      <c r="O85" s="1" t="s">
-        <v>101</v>
+        <v>434</v>
+      </c>
+      <c r="O85" t="s">
+        <v>100</v>
       </c>
       <c r="P85" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B86" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C86" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D86">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2019</v>
       </c>
+      <c r="E86" t="s">
+        <v>437</v>
+      </c>
+      <c r="F86" t="s">
+        <v>471</v>
+      </c>
+      <c r="G86" t="s">
+        <v>299</v>
+      </c>
+      <c r="H86">
+        <v>54</v>
+      </c>
+      <c r="I86">
+        <v>3</v>
+      </c>
       <c r="M86" t="s">
-        <v>288</v>
-      </c>
-      <c r="O86" s="1" t="s">
-        <v>102</v>
+        <v>434</v>
+      </c>
+      <c r="O86" t="s">
+        <v>101</v>
       </c>
       <c r="P86" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B87" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C87" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D87">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2019</v>
       </c>
+      <c r="E87" t="s">
+        <v>472</v>
+      </c>
+      <c r="F87" t="s">
+        <v>473</v>
+      </c>
+      <c r="G87" t="s">
+        <v>299</v>
+      </c>
+      <c r="H87">
+        <v>54</v>
+      </c>
+      <c r="I87">
+        <v>3</v>
+      </c>
       <c r="M87" t="s">
-        <v>288</v>
-      </c>
-      <c r="O87" s="1" t="s">
-        <v>103</v>
+        <v>434</v>
+      </c>
+      <c r="O87" t="s">
+        <v>102</v>
       </c>
       <c r="P87" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B88" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C88" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D88">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2020</v>
       </c>
+      <c r="E88" t="s">
+        <v>474</v>
+      </c>
+      <c r="F88" t="s">
+        <v>475</v>
+      </c>
+      <c r="G88" t="s">
+        <v>299</v>
+      </c>
+      <c r="H88">
+        <v>55</v>
+      </c>
+      <c r="I88">
+        <v>6</v>
+      </c>
       <c r="M88" t="s">
-        <v>288</v>
-      </c>
-      <c r="O88" s="1" t="s">
-        <v>104</v>
+        <v>434</v>
+      </c>
+      <c r="O88" t="s">
+        <v>103</v>
       </c>
       <c r="P88" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B89" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C89" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D89">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2020</v>
       </c>
+      <c r="E89" t="s">
+        <v>476</v>
+      </c>
+      <c r="F89" t="s">
+        <v>478</v>
+      </c>
+      <c r="G89" t="s">
+        <v>299</v>
+      </c>
+      <c r="H89">
+        <v>55</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+      <c r="J89" t="s">
+        <v>479</v>
+      </c>
       <c r="M89" t="s">
-        <v>288</v>
-      </c>
-      <c r="O89" s="1" t="s">
-        <v>105</v>
+        <v>434</v>
+      </c>
+      <c r="O89" t="s">
+        <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B90" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C90" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D90">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2020</v>
       </c>
+      <c r="E90" t="s">
+        <v>480</v>
+      </c>
+      <c r="F90" t="s">
+        <v>481</v>
+      </c>
+      <c r="G90" t="s">
+        <v>482</v>
+      </c>
+      <c r="H90">
+        <v>11</v>
+      </c>
+      <c r="I90">
+        <v>2</v>
+      </c>
+      <c r="J90" t="s">
+        <v>483</v>
+      </c>
       <c r="M90" t="s">
-        <v>288</v>
-      </c>
-      <c r="O90" s="1" t="s">
-        <v>106</v>
+        <v>434</v>
+      </c>
+      <c r="O90" t="s">
+        <v>105</v>
       </c>
       <c r="P90" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B91" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C91" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D91">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2020</v>
       </c>
+      <c r="E91" t="s">
+        <v>484</v>
+      </c>
+      <c r="F91" t="s">
+        <v>485</v>
+      </c>
+      <c r="G91" t="s">
+        <v>426</v>
+      </c>
+      <c r="H91">
+        <v>32</v>
+      </c>
+      <c r="I91">
+        <v>1</v>
+      </c>
+      <c r="J91" t="s">
+        <v>486</v>
+      </c>
       <c r="M91" t="s">
-        <v>288</v>
-      </c>
-      <c r="O91" s="1" t="s">
-        <v>107</v>
+        <v>434</v>
+      </c>
+      <c r="O91" t="s">
+        <v>106</v>
       </c>
       <c r="P91" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B92" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C92" t="s">
-        <v>287</v>
+        <v>467</v>
       </c>
       <c r="D92">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2021</v>
       </c>
+      <c r="E92" t="s">
+        <v>487</v>
+      </c>
+      <c r="F92" t="s">
+        <v>488</v>
+      </c>
+      <c r="G92" t="s">
+        <v>489</v>
+      </c>
+      <c r="H92">
+        <v>147</v>
+      </c>
+      <c r="I92">
+        <v>2</v>
+      </c>
       <c r="M92" t="s">
-        <v>288</v>
-      </c>
-      <c r="O92" s="1" t="s">
-        <v>108</v>
+        <v>434</v>
+      </c>
+      <c r="O92" t="s">
+        <v>107</v>
       </c>
       <c r="P92" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B93" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C93" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D93">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2021</v>
       </c>
+      <c r="E93" t="s">
+        <v>490</v>
+      </c>
+      <c r="F93" t="s">
+        <v>491</v>
+      </c>
+      <c r="G93" t="s">
+        <v>299</v>
+      </c>
+      <c r="H93">
+        <v>56</v>
+      </c>
+      <c r="I93">
+        <v>4</v>
+      </c>
+      <c r="J93" t="s">
+        <v>492</v>
+      </c>
       <c r="M93" t="s">
-        <v>288</v>
-      </c>
-      <c r="O93" s="1" t="s">
-        <v>109</v>
+        <v>434</v>
+      </c>
+      <c r="O93" t="s">
+        <v>108</v>
       </c>
       <c r="P93" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B94" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C94" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D94">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2021</v>
       </c>
+      <c r="E94" t="s">
+        <v>470</v>
+      </c>
+      <c r="F94" t="s">
+        <v>494</v>
+      </c>
+      <c r="G94" t="s">
+        <v>299</v>
+      </c>
+      <c r="H94">
+        <v>56</v>
+      </c>
+      <c r="I94">
+        <v>1</v>
+      </c>
       <c r="M94" t="s">
-        <v>288</v>
-      </c>
-      <c r="O94" s="1" t="s">
-        <v>110</v>
+        <v>434</v>
+      </c>
+      <c r="O94" t="s">
+        <v>493</v>
       </c>
       <c r="P94" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B95" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C95" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D95">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2021</v>
       </c>
+      <c r="E95" t="s">
+        <v>477</v>
+      </c>
+      <c r="F95" t="s">
+        <v>496</v>
+      </c>
+      <c r="G95" t="s">
+        <v>299</v>
+      </c>
+      <c r="H95">
+        <v>56</v>
+      </c>
+      <c r="I95">
+        <v>1</v>
+      </c>
       <c r="M95" t="s">
-        <v>288</v>
-      </c>
-      <c r="O95" s="1" t="s">
-        <v>111</v>
+        <v>434</v>
+      </c>
+      <c r="O95" t="s">
+        <v>495</v>
       </c>
       <c r="P95" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B96" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C96" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D96">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2021</v>
       </c>
+      <c r="E96" t="s">
+        <v>498</v>
+      </c>
+      <c r="F96" t="s">
+        <v>499</v>
+      </c>
+      <c r="G96" t="s">
+        <v>299</v>
+      </c>
+      <c r="H96">
+        <v>56</v>
+      </c>
+      <c r="I96">
+        <v>7</v>
+      </c>
       <c r="M96" t="s">
-        <v>288</v>
-      </c>
-      <c r="O96" s="1" t="s">
-        <v>112</v>
+        <v>434</v>
+      </c>
+      <c r="O96" t="s">
+        <v>497</v>
       </c>
       <c r="P96" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B97" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C97" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D97">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2021</v>
       </c>
+      <c r="E97" t="s">
+        <v>500</v>
+      </c>
+      <c r="F97" t="s">
+        <v>501</v>
+      </c>
+      <c r="G97" t="s">
+        <v>299</v>
+      </c>
+      <c r="H97">
+        <v>56</v>
+      </c>
+      <c r="I97">
+        <v>4</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>502</v>
+      </c>
       <c r="M97" t="s">
-        <v>288</v>
-      </c>
-      <c r="O97" s="1" t="s">
-        <v>113</v>
+        <v>434</v>
+      </c>
+      <c r="O97" t="s">
+        <v>112</v>
       </c>
       <c r="P97" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B98" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C98" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D98">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2021</v>
       </c>
+      <c r="E98" t="s">
+        <v>503</v>
+      </c>
+      <c r="F98" t="s">
+        <v>504</v>
+      </c>
+      <c r="G98" t="s">
+        <v>482</v>
+      </c>
+      <c r="H98">
+        <v>12</v>
+      </c>
+      <c r="I98">
+        <v>2</v>
+      </c>
+      <c r="J98" t="s">
+        <v>505</v>
+      </c>
       <c r="M98" t="s">
-        <v>288</v>
-      </c>
-      <c r="O98" s="1" t="s">
-        <v>114</v>
+        <v>434</v>
+      </c>
+      <c r="O98" t="s">
+        <v>113</v>
       </c>
       <c r="P98" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B99" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C99" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D99">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2021</v>
       </c>
+      <c r="E99" t="s">
+        <v>503</v>
+      </c>
+      <c r="F99" t="s">
+        <v>506</v>
+      </c>
+      <c r="G99" t="s">
+        <v>299</v>
+      </c>
+      <c r="H99">
+        <v>56</v>
+      </c>
+      <c r="I99">
+        <v>5</v>
+      </c>
+      <c r="J99" s="3" t="s">
+        <v>507</v>
+      </c>
       <c r="M99" t="s">
-        <v>288</v>
-      </c>
-      <c r="O99" s="1" t="s">
-        <v>115</v>
+        <v>434</v>
+      </c>
+      <c r="O99" t="s">
+        <v>114</v>
       </c>
       <c r="P99" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B100" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C100" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D100">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2021</v>
       </c>
+      <c r="E100" t="s">
+        <v>508</v>
+      </c>
+      <c r="F100" t="s">
+        <v>509</v>
+      </c>
+      <c r="G100" t="s">
+        <v>299</v>
+      </c>
+      <c r="H100">
+        <v>56</v>
+      </c>
+      <c r="I100">
+        <v>7</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>502</v>
+      </c>
       <c r="M100" t="s">
-        <v>288</v>
-      </c>
-      <c r="O100" s="1" t="s">
-        <v>116</v>
+        <v>434</v>
+      </c>
+      <c r="O100" t="s">
+        <v>115</v>
       </c>
       <c r="P100" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B101" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C101" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D101">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2021</v>
       </c>
+      <c r="E101" t="s">
+        <v>510</v>
+      </c>
+      <c r="F101" t="s">
+        <v>511</v>
+      </c>
+      <c r="G101" t="s">
+        <v>299</v>
+      </c>
+      <c r="H101">
+        <v>56</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>512</v>
+      </c>
       <c r="M101" t="s">
-        <v>288</v>
-      </c>
-      <c r="O101" s="1" t="s">
-        <v>117</v>
+        <v>434</v>
+      </c>
+      <c r="O101" t="s">
+        <v>116</v>
       </c>
       <c r="P101" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B102" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C102" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D102">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2021</v>
       </c>
+      <c r="E102" t="s">
+        <v>513</v>
+      </c>
+      <c r="F102" t="s">
+        <v>514</v>
+      </c>
+      <c r="G102" t="s">
+        <v>482</v>
+      </c>
+      <c r="H102">
+        <v>12</v>
+      </c>
+      <c r="I102">
+        <v>3</v>
+      </c>
+      <c r="J102" t="s">
+        <v>515</v>
+      </c>
       <c r="M102" t="s">
-        <v>288</v>
-      </c>
-      <c r="O102" s="1" t="s">
-        <v>118</v>
+        <v>434</v>
+      </c>
+      <c r="O102" t="s">
+        <v>117</v>
       </c>
       <c r="P102" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B103" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C103" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D103">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2021</v>
       </c>
+      <c r="E103" t="s">
+        <v>516</v>
+      </c>
+      <c r="F103" t="s">
+        <v>517</v>
+      </c>
+      <c r="G103" t="s">
+        <v>299</v>
+      </c>
+      <c r="H103">
+        <v>56</v>
+      </c>
+      <c r="I103">
+        <v>2</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>512</v>
+      </c>
       <c r="M103" t="s">
-        <v>288</v>
-      </c>
-      <c r="O103" s="1" t="s">
-        <v>119</v>
+        <v>434</v>
+      </c>
+      <c r="O103" t="s">
+        <v>118</v>
       </c>
       <c r="P103" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B104" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C104" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D104">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2021</v>
       </c>
+      <c r="E104" t="s">
+        <v>518</v>
+      </c>
+      <c r="F104" t="s">
+        <v>521</v>
+      </c>
+      <c r="G104" t="s">
+        <v>299</v>
+      </c>
+      <c r="H104">
+        <v>56</v>
+      </c>
+      <c r="I104">
+        <v>6</v>
+      </c>
+      <c r="J104" t="s">
+        <v>522</v>
+      </c>
       <c r="M104" t="s">
-        <v>288</v>
-      </c>
-      <c r="O104" s="1" t="s">
-        <v>120</v>
+        <v>434</v>
+      </c>
+      <c r="O104" t="s">
+        <v>119</v>
       </c>
       <c r="P104" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B105" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C105" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D105">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2021</v>
       </c>
+      <c r="E105" t="s">
+        <v>476</v>
+      </c>
+      <c r="F105" t="s">
+        <v>519</v>
+      </c>
+      <c r="G105" t="s">
+        <v>299</v>
+      </c>
+      <c r="H105">
+        <v>56</v>
+      </c>
+      <c r="I105">
+        <v>5</v>
+      </c>
+      <c r="J105" t="s">
+        <v>520</v>
+      </c>
       <c r="M105" t="s">
-        <v>288</v>
-      </c>
-      <c r="O105" s="1" t="s">
-        <v>121</v>
+        <v>434</v>
+      </c>
+      <c r="O105" t="s">
+        <v>120</v>
       </c>
       <c r="P105" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B106" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C106" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D106">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2021</v>
       </c>
+      <c r="E106" t="s">
+        <v>523</v>
+      </c>
+      <c r="F106" t="s">
+        <v>524</v>
+      </c>
+      <c r="G106" t="s">
+        <v>482</v>
+      </c>
+      <c r="H106">
+        <v>12</v>
+      </c>
+      <c r="I106">
+        <v>2</v>
+      </c>
+      <c r="J106" t="s">
+        <v>525</v>
+      </c>
       <c r="M106" t="s">
-        <v>288</v>
-      </c>
-      <c r="O106" s="1" t="s">
-        <v>122</v>
+        <v>434</v>
+      </c>
+      <c r="O106" t="s">
+        <v>121</v>
       </c>
       <c r="P106" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B107" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C107" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D107">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2022</v>
       </c>
+      <c r="E107" t="s">
+        <v>526</v>
+      </c>
+      <c r="F107" t="s">
+        <v>527</v>
+      </c>
+      <c r="G107" t="s">
+        <v>299</v>
+      </c>
+      <c r="H107">
+        <v>57</v>
+      </c>
+      <c r="I107">
+        <v>4</v>
+      </c>
       <c r="M107" t="s">
-        <v>288</v>
-      </c>
-      <c r="O107" s="1" t="s">
-        <v>123</v>
+        <v>434</v>
+      </c>
+      <c r="O107" t="s">
+        <v>122</v>
       </c>
       <c r="P107" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B108" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C108" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D108">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2022</v>
       </c>
+      <c r="E108" t="s">
+        <v>528</v>
+      </c>
+      <c r="F108" t="s">
+        <v>529</v>
+      </c>
+      <c r="G108" t="s">
+        <v>299</v>
+      </c>
+      <c r="H108">
+        <v>57</v>
+      </c>
+      <c r="I108">
+        <v>5</v>
+      </c>
+      <c r="J108" t="s">
+        <v>530</v>
+      </c>
       <c r="M108" t="s">
-        <v>288</v>
-      </c>
-      <c r="O108" s="1" t="s">
-        <v>124</v>
+        <v>434</v>
+      </c>
+      <c r="O108" t="s">
+        <v>123</v>
       </c>
       <c r="P108" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B109" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C109" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D109">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2022</v>
       </c>
+      <c r="E109" t="s">
+        <v>531</v>
+      </c>
+      <c r="F109" t="s">
+        <v>532</v>
+      </c>
+      <c r="G109" t="s">
+        <v>533</v>
+      </c>
+      <c r="H109">
+        <v>13</v>
+      </c>
+      <c r="I109">
+        <v>4</v>
+      </c>
+      <c r="J109" t="s">
+        <v>534</v>
+      </c>
       <c r="M109" t="s">
-        <v>288</v>
-      </c>
-      <c r="O109" s="1" t="s">
-        <v>125</v>
+        <v>434</v>
+      </c>
+      <c r="O109" t="s">
+        <v>124</v>
       </c>
       <c r="P109" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B110" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C110" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D110">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2022</v>
       </c>
+      <c r="E110" t="s">
+        <v>535</v>
+      </c>
+      <c r="F110" t="s">
+        <v>536</v>
+      </c>
+      <c r="G110" t="s">
+        <v>299</v>
+      </c>
+      <c r="H110">
+        <v>57</v>
+      </c>
+      <c r="I110">
+        <v>4</v>
+      </c>
       <c r="M110" t="s">
-        <v>288</v>
-      </c>
-      <c r="O110" s="1" t="s">
-        <v>126</v>
+        <v>434</v>
+      </c>
+      <c r="O110" t="s">
+        <v>125</v>
       </c>
       <c r="P110" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B111" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C111" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D111">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2022</v>
       </c>
+      <c r="E111" t="s">
+        <v>389</v>
+      </c>
+      <c r="F111" t="s">
+        <v>537</v>
+      </c>
+      <c r="G111" t="s">
+        <v>366</v>
+      </c>
+      <c r="H111">
+        <v>35</v>
+      </c>
+      <c r="I111">
+        <v>1</v>
+      </c>
       <c r="M111" t="s">
-        <v>288</v>
-      </c>
-      <c r="O111" s="1" t="s">
-        <v>127</v>
+        <v>434</v>
+      </c>
+      <c r="O111" t="s">
+        <v>126</v>
       </c>
       <c r="P111" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B112" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C112" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D112">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2022</v>
       </c>
+      <c r="E112" t="s">
+        <v>538</v>
+      </c>
+      <c r="F112" t="s">
+        <v>539</v>
+      </c>
+      <c r="G112" t="s">
+        <v>540</v>
+      </c>
+      <c r="H112">
+        <v>3</v>
+      </c>
+      <c r="I112">
+        <v>1</v>
+      </c>
+      <c r="J112" t="s">
+        <v>541</v>
+      </c>
       <c r="M112" t="s">
-        <v>288</v>
-      </c>
-      <c r="O112" s="1" t="s">
-        <v>128</v>
+        <v>434</v>
+      </c>
+      <c r="O112" t="s">
+        <v>127</v>
       </c>
       <c r="P112" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B113" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C113" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D113">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2022</v>
       </c>
+      <c r="E113" t="s">
+        <v>538</v>
+      </c>
+      <c r="F113" t="s">
+        <v>542</v>
+      </c>
+      <c r="G113" t="s">
+        <v>426</v>
+      </c>
+      <c r="H113">
+        <v>34</v>
+      </c>
+      <c r="I113">
+        <v>1</v>
+      </c>
+      <c r="J113" t="s">
+        <v>543</v>
+      </c>
       <c r="M113" t="s">
-        <v>288</v>
-      </c>
-      <c r="O113" s="1" t="s">
-        <v>129</v>
+        <v>434</v>
+      </c>
+      <c r="O113" t="s">
+        <v>128</v>
       </c>
       <c r="P113" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B114" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C114" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D114">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2022</v>
       </c>
+      <c r="E114" t="s">
+        <v>544</v>
+      </c>
+      <c r="F114" t="s">
+        <v>545</v>
+      </c>
+      <c r="G114" t="s">
+        <v>299</v>
+      </c>
+      <c r="H114">
+        <v>57</v>
+      </c>
+      <c r="I114">
+        <v>1</v>
+      </c>
+      <c r="J114" t="s">
+        <v>546</v>
+      </c>
       <c r="M114" t="s">
-        <v>288</v>
-      </c>
-      <c r="O114" s="1" t="s">
-        <v>130</v>
+        <v>434</v>
+      </c>
+      <c r="O114" t="s">
+        <v>129</v>
       </c>
       <c r="P114" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B115" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C115" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D115">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2022</v>
       </c>
+      <c r="E115" t="s">
+        <v>544</v>
+      </c>
+      <c r="F115" t="s">
+        <v>547</v>
+      </c>
+      <c r="G115" t="s">
+        <v>533</v>
+      </c>
+      <c r="H115">
+        <v>13</v>
+      </c>
+      <c r="I115">
+        <v>3</v>
+      </c>
       <c r="M115" t="s">
-        <v>288</v>
-      </c>
-      <c r="O115" s="1" t="s">
-        <v>131</v>
+        <v>434</v>
+      </c>
+      <c r="O115" t="s">
+        <v>130</v>
       </c>
       <c r="P115" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B116" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C116" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D116">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2022</v>
       </c>
+      <c r="E116" t="s">
+        <v>484</v>
+      </c>
+      <c r="F116" t="s">
+        <v>548</v>
+      </c>
+      <c r="G116" t="s">
+        <v>533</v>
+      </c>
+      <c r="H116">
+        <v>13</v>
+      </c>
+      <c r="I116">
+        <v>1</v>
+      </c>
       <c r="M116" t="s">
-        <v>288</v>
-      </c>
-      <c r="O116" s="1" t="s">
-        <v>132</v>
+        <v>434</v>
+      </c>
+      <c r="O116" t="s">
+        <v>131</v>
       </c>
       <c r="P116" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B117" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C117" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D117">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2023</v>
       </c>
+      <c r="E117" t="s">
+        <v>454</v>
+      </c>
+      <c r="F117" t="s">
+        <v>549</v>
+      </c>
+      <c r="G117" t="s">
+        <v>533</v>
+      </c>
+      <c r="H117">
+        <v>14</v>
+      </c>
+      <c r="I117">
+        <v>4</v>
+      </c>
+      <c r="J117" t="s">
+        <v>550</v>
+      </c>
       <c r="M117" t="s">
-        <v>288</v>
-      </c>
-      <c r="O117" s="1" t="s">
-        <v>133</v>
+        <v>434</v>
+      </c>
+      <c r="O117" t="s">
+        <v>132</v>
       </c>
       <c r="P117" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B118" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C118" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D118">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2023</v>
       </c>
+      <c r="E118" t="s">
+        <v>551</v>
+      </c>
+      <c r="F118" t="s">
+        <v>552</v>
+      </c>
+      <c r="G118" t="s">
+        <v>299</v>
+      </c>
+      <c r="H118">
+        <v>58</v>
+      </c>
+      <c r="I118">
+        <v>4</v>
+      </c>
+      <c r="J118" t="s">
+        <v>553</v>
+      </c>
       <c r="M118" t="s">
-        <v>288</v>
-      </c>
-      <c r="O118" s="1" t="s">
-        <v>134</v>
+        <v>434</v>
+      </c>
+      <c r="O118" t="s">
+        <v>133</v>
       </c>
       <c r="P118" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B119" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C119" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D119">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2023</v>
       </c>
+      <c r="E119" t="s">
+        <v>554</v>
+      </c>
+      <c r="F119" t="s">
+        <v>555</v>
+      </c>
+      <c r="G119" t="s">
+        <v>299</v>
+      </c>
+      <c r="H119">
+        <v>58</v>
+      </c>
+      <c r="I119">
+        <v>3</v>
+      </c>
+      <c r="J119" t="s">
+        <v>556</v>
+      </c>
       <c r="M119" t="s">
-        <v>288</v>
-      </c>
-      <c r="O119" s="1" t="s">
-        <v>135</v>
+        <v>434</v>
+      </c>
+      <c r="O119" t="s">
+        <v>134</v>
       </c>
       <c r="P119" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B120" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C120" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D120">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2023</v>
       </c>
+      <c r="E120" t="s">
+        <v>557</v>
+      </c>
+      <c r="F120" t="s">
+        <v>558</v>
+      </c>
+      <c r="G120" t="s">
+        <v>559</v>
+      </c>
+      <c r="H120">
+        <v>39</v>
+      </c>
+      <c r="I120">
+        <v>7</v>
+      </c>
+      <c r="J120" t="s">
+        <v>560</v>
+      </c>
       <c r="M120" t="s">
-        <v>288</v>
-      </c>
-      <c r="O120" s="1" t="s">
-        <v>136</v>
+        <v>434</v>
+      </c>
+      <c r="O120" t="s">
+        <v>135</v>
       </c>
       <c r="P120" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B121" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C121" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D121">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2023</v>
       </c>
+      <c r="E121" t="s">
+        <v>561</v>
+      </c>
+      <c r="F121" t="s">
+        <v>562</v>
+      </c>
+      <c r="G121" t="s">
+        <v>299</v>
+      </c>
+      <c r="H121">
+        <v>58</v>
+      </c>
+      <c r="I121">
+        <v>1</v>
+      </c>
+      <c r="J121" t="s">
+        <v>563</v>
+      </c>
       <c r="M121" t="s">
-        <v>288</v>
-      </c>
-      <c r="O121" s="1" t="s">
-        <v>137</v>
+        <v>434</v>
+      </c>
+      <c r="O121" t="s">
+        <v>136</v>
       </c>
       <c r="P121" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B122" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C122" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D122">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2023</v>
       </c>
+      <c r="E122" t="s">
+        <v>484</v>
+      </c>
+      <c r="F122" t="s">
+        <v>564</v>
+      </c>
+      <c r="G122" t="s">
+        <v>299</v>
+      </c>
+      <c r="H122">
+        <v>58</v>
+      </c>
+      <c r="I122">
+        <v>2</v>
+      </c>
+      <c r="J122" t="s">
+        <v>565</v>
+      </c>
       <c r="M122" t="s">
-        <v>288</v>
-      </c>
-      <c r="O122" s="1" t="s">
-        <v>138</v>
+        <v>434</v>
+      </c>
+      <c r="O122" t="s">
+        <v>137</v>
       </c>
       <c r="P122" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B123" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C123" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D123">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2023</v>
       </c>
+      <c r="E123" t="s">
+        <v>566</v>
+      </c>
+      <c r="F123" t="s">
+        <v>567</v>
+      </c>
+      <c r="G123" t="s">
+        <v>533</v>
+      </c>
+      <c r="H123">
+        <v>14</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+      <c r="J123" t="s">
+        <v>568</v>
+      </c>
       <c r="M123" t="s">
-        <v>288</v>
-      </c>
-      <c r="O123" s="1" t="s">
-        <v>139</v>
+        <v>434</v>
+      </c>
+      <c r="O123" t="s">
+        <v>138</v>
       </c>
       <c r="P123" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B124" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C124" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D124">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2024</v>
       </c>
+      <c r="E124" t="s">
+        <v>569</v>
+      </c>
+      <c r="F124" t="s">
+        <v>570</v>
+      </c>
+      <c r="G124" t="s">
+        <v>533</v>
+      </c>
+      <c r="H124">
+        <v>15</v>
+      </c>
+      <c r="I124">
+        <v>4</v>
+      </c>
+      <c r="J124" t="s">
+        <v>571</v>
+      </c>
       <c r="M124" t="s">
-        <v>288</v>
-      </c>
-      <c r="O124" s="1" t="s">
-        <v>140</v>
+        <v>434</v>
+      </c>
+      <c r="O124" t="s">
+        <v>139</v>
       </c>
       <c r="P124" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B125" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C125" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D125">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2024</v>
       </c>
+      <c r="E125" t="s">
+        <v>572</v>
+      </c>
+      <c r="F125" t="s">
+        <v>573</v>
+      </c>
+      <c r="G125" t="s">
+        <v>533</v>
+      </c>
+      <c r="H125">
+        <v>15</v>
+      </c>
+      <c r="I125">
+        <v>4</v>
+      </c>
+      <c r="J125" t="s">
+        <v>574</v>
+      </c>
       <c r="M125" t="s">
-        <v>288</v>
-      </c>
-      <c r="O125" s="1" t="s">
-        <v>141</v>
+        <v>434</v>
+      </c>
+      <c r="O125" t="s">
+        <v>140</v>
       </c>
       <c r="P125" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B126" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C126" t="s">
-        <v>287</v>
+        <v>467</v>
       </c>
       <c r="D126">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2024</v>
       </c>
+      <c r="E126" t="s">
+        <v>575</v>
+      </c>
+      <c r="F126" t="s">
+        <v>576</v>
+      </c>
+      <c r="G126" t="s">
+        <v>577</v>
+      </c>
+      <c r="H126">
+        <v>150</v>
+      </c>
       <c r="M126" t="s">
-        <v>288</v>
-      </c>
-      <c r="O126" s="1" t="s">
-        <v>142</v>
+        <v>434</v>
+      </c>
+      <c r="O126" t="s">
+        <v>141</v>
       </c>
       <c r="P126" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B127" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C127" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D127">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2024</v>
       </c>
+      <c r="E127" t="s">
+        <v>557</v>
+      </c>
+      <c r="F127" t="s">
+        <v>578</v>
+      </c>
+      <c r="G127" t="s">
+        <v>533</v>
+      </c>
+      <c r="H127">
+        <v>15</v>
+      </c>
+      <c r="I127">
+        <v>2</v>
+      </c>
+      <c r="J127" t="s">
+        <v>579</v>
+      </c>
       <c r="M127" t="s">
-        <v>288</v>
-      </c>
-      <c r="O127" s="1" t="s">
-        <v>143</v>
+        <v>434</v>
+      </c>
+      <c r="O127" t="s">
+        <v>142</v>
       </c>
       <c r="P127" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q127" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B128" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C128" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D128">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2024</v>
       </c>
+      <c r="E128" t="s">
+        <v>557</v>
+      </c>
+      <c r="F128" t="s">
+        <v>580</v>
+      </c>
+      <c r="G128" t="s">
+        <v>299</v>
+      </c>
+      <c r="H128">
+        <v>59</v>
+      </c>
+      <c r="I128">
+        <v>6</v>
+      </c>
       <c r="M128" t="s">
-        <v>288</v>
-      </c>
-      <c r="O128" s="1" t="s">
-        <v>144</v>
+        <v>434</v>
+      </c>
+      <c r="O128" t="s">
+        <v>143</v>
       </c>
       <c r="P128" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q128" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B129" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C129" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D129">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2024</v>
       </c>
+      <c r="E129" t="s">
+        <v>581</v>
+      </c>
+      <c r="F129" t="s">
+        <v>582</v>
+      </c>
+      <c r="G129" t="s">
+        <v>533</v>
+      </c>
+      <c r="H129">
+        <v>15</v>
+      </c>
+      <c r="I129">
+        <v>3</v>
+      </c>
+      <c r="J129" s="3" t="s">
+        <v>583</v>
+      </c>
       <c r="M129" t="s">
+        <v>434</v>
+      </c>
+      <c r="O129" t="s">
+        <v>144</v>
+      </c>
+      <c r="P129" t="s">
         <v>288</v>
-      </c>
-      <c r="O129" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="P129" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B130" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C130" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D130">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2025</v>
       </c>
+      <c r="E130" t="s">
+        <v>584</v>
+      </c>
+      <c r="F130" t="s">
+        <v>585</v>
+      </c>
+      <c r="G130" t="s">
+        <v>533</v>
+      </c>
+      <c r="H130">
+        <v>16</v>
+      </c>
+      <c r="I130">
+        <v>3</v>
+      </c>
+      <c r="J130" t="s">
+        <v>586</v>
+      </c>
       <c r="M130" t="s">
-        <v>288</v>
-      </c>
-      <c r="O130" s="1" t="s">
-        <v>146</v>
+        <v>434</v>
+      </c>
+      <c r="O130" t="s">
+        <v>145</v>
       </c>
       <c r="P130" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B131" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C131" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D131">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2025</v>
       </c>
+      <c r="E131" t="s">
+        <v>587</v>
+      </c>
+      <c r="F131" t="s">
+        <v>588</v>
+      </c>
+      <c r="G131" t="s">
+        <v>533</v>
+      </c>
+      <c r="H131">
+        <v>16</v>
+      </c>
+      <c r="I131">
+        <v>4</v>
+      </c>
+      <c r="J131" t="s">
+        <v>486</v>
+      </c>
       <c r="M131" t="s">
-        <v>288</v>
-      </c>
-      <c r="O131" s="1" t="s">
-        <v>147</v>
+        <v>434</v>
+      </c>
+      <c r="O131" t="s">
+        <v>146</v>
       </c>
       <c r="P131" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B132" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C132" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D132">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2025</v>
       </c>
+      <c r="E132" t="s">
+        <v>589</v>
+      </c>
+      <c r="F132" t="s">
+        <v>590</v>
+      </c>
+      <c r="G132" t="s">
+        <v>591</v>
+      </c>
+      <c r="H132">
+        <v>125</v>
+      </c>
+      <c r="J132" t="s">
+        <v>592</v>
+      </c>
       <c r="M132" t="s">
-        <v>288</v>
-      </c>
-      <c r="O132" s="1" t="s">
-        <v>148</v>
+        <v>434</v>
+      </c>
+      <c r="O132" t="s">
+        <v>147</v>
       </c>
       <c r="P132" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B133" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C133" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D133">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2025</v>
       </c>
+      <c r="E133" t="s">
+        <v>589</v>
+      </c>
+      <c r="F133" t="s">
+        <v>593</v>
+      </c>
+      <c r="G133" t="s">
+        <v>533</v>
+      </c>
+      <c r="H133">
+        <v>16</v>
+      </c>
+      <c r="I133">
+        <v>1</v>
+      </c>
+      <c r="J133" t="s">
+        <v>594</v>
+      </c>
       <c r="M133" t="s">
-        <v>288</v>
-      </c>
-      <c r="O133" s="1" t="s">
-        <v>149</v>
+        <v>434</v>
+      </c>
+      <c r="O133" t="s">
+        <v>148</v>
       </c>
       <c r="P133" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="134" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B134" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C134" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D134">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2025</v>
       </c>
+      <c r="E134" t="s">
+        <v>595</v>
+      </c>
+      <c r="F134" t="s">
+        <v>596</v>
+      </c>
+      <c r="G134" t="s">
+        <v>533</v>
+      </c>
+      <c r="H134">
+        <v>16</v>
+      </c>
+      <c r="I134">
+        <v>4</v>
+      </c>
+      <c r="J134" t="s">
+        <v>597</v>
+      </c>
       <c r="M134" t="s">
-        <v>288</v>
-      </c>
-      <c r="O134" s="1" t="s">
-        <v>150</v>
+        <v>434</v>
+      </c>
+      <c r="O134" t="s">
+        <v>149</v>
       </c>
       <c r="P134" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B135" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C135" t="s">
-        <v>287</v>
+        <v>600</v>
       </c>
       <c r="D135">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2025</v>
       </c>
+      <c r="E135" t="s">
+        <v>476</v>
+      </c>
+      <c r="F135" t="s">
+        <v>598</v>
+      </c>
+      <c r="G135" t="s">
+        <v>533</v>
+      </c>
+      <c r="H135">
+        <v>16</v>
+      </c>
+      <c r="I135">
+        <v>2</v>
+      </c>
+      <c r="J135" s="1" t="s">
+        <v>599</v>
+      </c>
       <c r="M135" t="s">
-        <v>288</v>
-      </c>
-      <c r="O135" s="1" t="s">
-        <v>151</v>
+        <v>434</v>
+      </c>
+      <c r="O135" t="s">
+        <v>150</v>
       </c>
       <c r="P135" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -6229,677 +8044,677 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="1" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="1" t="s">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="1" t="s">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="1" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="1" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="1" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="1" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="1" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="1" t="s">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="1" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="1" t="s">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="1" t="s">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="1" t="s">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="1" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="1" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="1" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="1" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="1" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="1" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="1" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="1" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="1" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="1" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="1" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="1" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="1" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" s="1" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" s="1" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" s="1" t="s">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" s="1" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="1" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="1" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="1" t="s">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="1" t="s">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" s="1" t="s">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" s="1" t="s">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" s="1" t="s">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" s="1" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" s="1" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" s="1" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="1" t="s">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" s="1" t="s">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" s="1" t="s">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" s="1" t="s">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" s="1" t="s">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" s="1" t="s">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" s="1" t="s">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" s="1" t="s">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" s="1" t="s">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" s="1" t="s">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" s="1" t="s">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A102" s="1" t="s">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A103" s="1" t="s">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A104" s="1" t="s">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A105" s="1" t="s">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A106" s="1" t="s">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A107" s="1" t="s">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A108" s="1" t="s">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A109" s="1" t="s">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A110" s="1" t="s">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A111" s="1" t="s">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A112" s="1" t="s">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A113" s="1" t="s">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A114" s="1" t="s">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A115" s="1" t="s">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A116" s="1" t="s">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A117" s="1" t="s">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A118" s="1" t="s">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A119" s="1" t="s">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A120" s="1" t="s">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A121" s="1" t="s">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A122" s="1" t="s">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A123" s="1" t="s">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A124" s="1" t="s">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A125" s="1" t="s">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A126" s="1" t="s">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A127" s="1" t="s">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A128" s="1" t="s">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A129" s="1" t="s">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A130" s="1" t="s">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A131" s="1" t="s">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A132" s="1" t="s">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A133" s="1" t="s">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A134" s="1" t="s">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
         <v>150</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A135" s="1" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SmartCity20\.gemini\antigravity\scratch\surd-lab-homepage\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C3F26E-D3DC-4B3D-AEA3-9732C8DDF321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686A9505-5DA0-494C-BC72-76650D6F07B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{FB3B5A28-B30A-4FB9-B973-DA7691D44842}"/>
+    <workbookView xWindow="25800" yWindow="0" windowWidth="25800" windowHeight="21000" xr2:uid="{FB3B5A28-B30A-4FB9-B973-DA7691D44842}"/>
   </bookViews>
   <sheets>
     <sheet name="publications" sheetId="1" r:id="rId1"/>
@@ -3099,10 +3099,10 @@
         <v>161</v>
       </c>
       <c r="B12" t="s">
-        <v>602</v>
+        <v>285</v>
       </c>
       <c r="C12" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D12">
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
@@ -3138,7 +3138,7 @@
         <v>162</v>
       </c>
       <c r="B13" t="s">
-        <v>285</v>
+        <v>602</v>
       </c>
       <c r="C13" t="s">
         <v>601</v>
